--- a/docs/flow.xlsx
+++ b/docs/flow.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alessandro\projects\autoprogram\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94BCEC3F-D5F4-4E87-BDC1-91949DDC2C42}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9D44523-A6F2-4743-A2FA-67993997AE89}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>user selects family</t>
   </si>
@@ -97,6 +97,9 @@
   </si>
   <si>
     <t>val</t>
+  </si>
+  <si>
+    <t>create or update</t>
   </si>
 </sst>
 </file>
@@ -140,9 +143,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -423,7 +427,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32.7109375" customWidth="1"/>
@@ -443,8 +447,8 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>7</v>
+      <c r="A2" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="F2" t="s">
         <v>15</v>
@@ -455,7 +459,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
         <v>16</v>
@@ -466,7 +470,7 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="s">
         <v>17</v>
@@ -477,7 +481,7 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H5" t="s">
         <v>22</v>
@@ -485,7 +489,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H6" t="s">
         <v>23</v>
@@ -493,41 +497,46 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>12</v>
       </c>
     </row>
